--- a/DATA/MODELADO/Bitacoras/Exp01-V3/bitacora_maestra_experimentos.xlsx
+++ b/DATA/MODELADO/Bitacoras/Exp01-V3/bitacora_maestra_experimentos.xlsx
@@ -597,11 +597,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Exp01-V2</t>
+          <t>Exp01</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46233.86601913194</v>
+        <v>46245.78630488426</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Escalado MinMax</t>
+          <t>RobustScaler</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -657,61 +657,61 @@
         <v>100</v>
       </c>
       <c r="R2" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02205953747034073</v>
+        <v>0.01507571898400784</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3111846446990967</v>
+        <v>0.6383737921714783</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9423301815986633</v>
+        <v>0.3085009157657623</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9944598078727722</v>
+        <v>0.997032642364502</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9350649118423462</v>
+        <v>0.8571428656578064</v>
       </c>
       <c r="X2" t="n">
-        <v>0.8461538553237915</v>
+        <v>0.9358974099159241</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.9358974358974359</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="AC2" t="n">
         <v>1</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.5</v>
+        <v>0.7916666666666667</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>MODELO NO APTO PARA DETECTAR OBJETIVO</t>
+          <t>Excelente</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>14.22514295578003</v>
+        <v>6.910932540893555</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Exp01-V3</t>
+          <t>Exp01</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46233.89164225687</v>
+        <v>46245.79172948754</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Escalado MinMax</t>
+          <t>RobustScaler</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -767,51 +767,51 @@
         <v>100</v>
       </c>
       <c r="R3" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05206235498189926</v>
+        <v>0.02133559994399548</v>
       </c>
       <c r="T3" t="n">
-        <v>1.122428059577942</v>
+        <v>0.5990229249000549</v>
       </c>
       <c r="U3" t="n">
-        <v>0.175503134727478</v>
+        <v>0.4188686311244965</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9940652847290039</v>
+        <v>0.9955489635467529</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9090909361839294</v>
+        <v>0.8701298832893372</v>
       </c>
       <c r="X3" t="n">
-        <v>0.9102563858032227</v>
+        <v>0.9487179517745972</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.9102564102564102</v>
+        <v>0.9487179487179487</v>
       </c>
       <c r="Z3" t="n">
         <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.8</v>
       </c>
       <c r="AC3" t="n">
         <v>1</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>MODELO APROBADO</t>
+          <t>Excelente</t>
         </is>
       </c>
       <c r="AF3" t="n">
-        <v>7.355789422988892</v>
+        <v>19.00173687934875</v>
       </c>
     </row>
   </sheetData>
